--- a/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD07350F-7A4A-450A-A12D-61DF2677A6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="98">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -178,12 +192,6 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10698904</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>124 Store Management (Gazuv Pemiku (10671950))</t>
   </si>
   <si>
@@ -281,9 +289,6 @@
   </si>
   <si>
     <t>Test_2</t>
-  </si>
-  <si>
-    <t>10698905</t>
   </si>
   <si>
     <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
@@ -322,81 +327,81 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="11"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FFFF0000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FF040C28"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
       <u/>
+      <sz val="14"/>
       <color theme="10"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FF4A4A4A"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="14"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <sz val="14"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <u/>
+      <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -408,7 +413,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.5999938962981048"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -419,7 +424,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.7999816888943144"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -451,8 +456,12 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -462,15 +471,25 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -481,7 +500,9 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -496,9 +517,15 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -904,9 +931,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BD3"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" customWidth="1"/>
@@ -964,7 +991,7 @@
     <col min="57" max="57" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:56" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1134,99 +1161,94 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:56" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>53</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="7"/>
+      <c r="D2" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="E2" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="F2" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="G2" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="I2" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="J2" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="K2" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="L2" s="14">
+        <f ca="1">TODAY()-31</f>
+        <v>45761</v>
+      </c>
+      <c r="M2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="N2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="P2" s="15" t="s">
         <v>63</v>
-      </c>
-      <c r="L2" s="14">
-        <f>TODAY()-31</f>
-        <v>45752</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="N2" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="O2" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="P2" s="15" t="s">
-        <v>65</v>
       </c>
       <c r="Q2" s="16">
         <v>21201</v>
       </c>
       <c r="R2" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="S2" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="U2" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="V2" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="S2" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="T2" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="U2" s="17" t="s">
+      <c r="W2" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="X2" s="19">
+        <f ca="1">L2</f>
+        <v>45761</v>
+      </c>
+      <c r="Y2" s="14">
+        <f ca="1">TODAY()+20</f>
+        <v>45812</v>
+      </c>
+      <c r="Z2" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="V2" s="18" t="s">
+      <c r="AA2" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="W2" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="X2" s="19">
-        <f>L2</f>
-        <v>45752</v>
-      </c>
-      <c r="Y2" s="14">
-        <f>TODAY()+20</f>
-        <v>45803</v>
-      </c>
-      <c r="Z2" s="20" t="s">
+      <c r="AB2" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AC2" s="23" t="s">
         <v>70</v>
       </c>
-      <c r="AB2" s="22" t="s">
+      <c r="AD2" s="22" t="s">
         <v>71</v>
-      </c>
-      <c r="AC2" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD2" s="22" t="s">
-        <v>73</v>
       </c>
       <c r="AE2" s="24">
         <v>124</v>
@@ -1235,284 +1257,262 @@
         <v>47</v>
       </c>
       <c r="AG2" s="24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AH2" s="25">
         <v>40</v>
       </c>
       <c r="AI2" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="AJ2" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK2" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL2" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="AJ2" s="22" t="s">
+      <c r="AM2" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="AK2" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL2" s="13" t="s">
+      <c r="AN2" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="AM2" s="13" t="s">
+      <c r="AO2" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="AN2" s="22" t="s">
+      <c r="AP2" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="AO2" s="26" t="s">
+      <c r="AQ2" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="AR2" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="AP2" s="9" t="s">
+      <c r="AS2" s="28">
+        <f t="array" aca="1" ref="AS2:AS3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>358004907</v>
+      </c>
+      <c r="AT2" s="22" t="s">
         <v>81</v>
-      </c>
-      <c r="AQ2" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="AR2" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="AS2" s="28">
-        <f t="array" ref="AS2:AS3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>738258649</v>
-      </c>
-      <c r="AT2" s="22" t="s">
-        <v>83</v>
       </c>
       <c r="AU2" s="29">
         <v>35591</v>
       </c>
       <c r="AV2" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AW2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AX2" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AY2" s="9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ2" s="30">
         <v>54057</v>
       </c>
       <c r="BA2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="BB2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>84</v>
+      </c>
+      <c r="BD2" t="s">
         <v>85</v>
       </c>
-      <c r="BC2" t="s">
+    </row>
+    <row r="3" spans="1:56" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>86</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="C3" s="7"/>
+      <c r="D3" s="8" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E3" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="B3" t="s">
+      <c r="H3" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="I3" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="L3" s="34">
+        <f t="shared" ref="L3" ca="1" si="0">TODAY()-31</f>
+        <v>45761</v>
+      </c>
+      <c r="M3" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="J3" s="26" t="s">
+      <c r="N3" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="P3" s="35" t="s">
         <v>63</v>
-      </c>
-      <c r="L3" s="34">
-        <f t="shared" ref="L3" si="0">TODAY()-31</f>
-        <v>45752</v>
-      </c>
-      <c r="M3" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="O3" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="P3" s="35" t="s">
-        <v>65</v>
       </c>
       <c r="Q3" s="16">
         <v>21201</v>
       </c>
       <c r="R3" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="S3" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="T3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="U3" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="V3" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="S3" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="T3" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="U3" s="26" t="s">
+      <c r="W3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="X3" s="19">
+        <f t="shared" ref="X3" ca="1" si="1">L3</f>
+        <v>45761</v>
+      </c>
+      <c r="Y3" s="34">
+        <f t="shared" ref="Y3" ca="1" si="2">TODAY()+20</f>
+        <v>45812</v>
+      </c>
+      <c r="Z3" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="V3" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="W3" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="X3" s="19">
-        <f t="shared" ref="X3" si="1">L3</f>
-        <v>45752</v>
-      </c>
-      <c r="Y3" s="34">
-        <f t="shared" ref="Y3" si="2">TODAY()+20</f>
-        <v>45803</v>
-      </c>
-      <c r="Z3" s="37" t="s">
-        <v>69</v>
-      </c>
       <c r="AA3" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB3" s="39" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC3" s="40" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD3" s="39" t="s">
         <v>93</v>
-      </c>
-      <c r="AB3" s="39" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC3" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD3" s="39" t="s">
-        <v>96</v>
       </c>
       <c r="AE3" s="41">
         <v>121</v>
       </c>
       <c r="AF3" s="42" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AG3" s="24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AH3" s="43">
         <v>10</v>
       </c>
       <c r="AI3" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="AJ3" s="39" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK3" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL3" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="AJ3" s="39" t="s">
-        <v>76</v>
-      </c>
-      <c r="AK3" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="AL3" s="26" t="s">
-        <v>77</v>
-      </c>
       <c r="AM3" s="26" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AN3" s="39" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="AO3" s="26" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AP3" s="26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="AQ3" s="26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AR3" s="26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AS3" s="45">
-        <v>283269566</v>
+        <f ca="1"/>
+        <v>573519542</v>
       </c>
       <c r="AT3" s="39" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="AU3" s="46">
         <v>35226</v>
       </c>
       <c r="AV3" s="26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AW3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AX3" s="26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="AY3" s="26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AZ3" s="30">
         <v>54057</v>
       </c>
       <c r="BA3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="BB3" t="s">
+        <v>83</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>84</v>
+      </c>
+      <c r="BD3" t="s">
         <v>85</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>86</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 Z2 W2 T2" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3">
-      <formula1>INDIRECT($G3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3">
-      <formula1>INDIRECT($G3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3">
-      <formula1>INDIRECT($G3)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2">
-      <formula1>INDIRECT($E2)</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 Z3 W3 T3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>INDIRECT($G3)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1"/>
-    <hyperlink ref="V3" r:id="rId2"/>
+    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
@@ -1,34 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD07350F-7A4A-450A-A12D-61DF2677A6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="101">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -192,6 +178,12 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t>10699096</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
     <t>124 Store Management (Gazuv Pemiku (10671950))</t>
   </si>
   <si>
@@ -201,10 +193,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Blake</t>
-  </si>
-  <si>
-    <t>Frami</t>
+    <t>Mariah</t>
+  </si>
+  <si>
+    <t>Tromp</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -234,7 +226,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 10007646</t>
+    <t>Auto 88181467</t>
   </si>
   <si>
     <t>Regular</t>
@@ -291,13 +283,16 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t>10699097</t>
+  </si>
+  <si>
     <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
   </si>
   <si>
-    <t>Abagail</t>
-  </si>
-  <si>
-    <t>Luettgen</t>
+    <t>Ewell</t>
+  </si>
+  <si>
+    <t>Bernhard</t>
   </si>
   <si>
     <t>No</t>
@@ -327,81 +322,81 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF040C28"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FF040C28"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
+      <color theme="10"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF4A4A4A"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FF4A4A4A"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="7">
@@ -413,7 +408,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.5999938962981048"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -424,7 +419,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -456,12 +451,8 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -471,25 +462,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -500,9 +481,7 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -517,15 +496,9 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
@@ -931,9 +904,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BD3"/>
-  <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" customWidth="1"/>
@@ -991,7 +964,7 @@
     <col min="57" max="57" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:56" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="18" customHeight="1" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1161,94 +1134,99 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:56" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="7"/>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>55</v>
+      </c>
       <c r="D2" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G2" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="14">
+        <f>TODAY()-31</f>
+        <v>45761</v>
+      </c>
+      <c r="M2" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="L2" s="14">
-        <f ca="1">TODAY()-31</f>
-        <v>45761</v>
-      </c>
-      <c r="M2" s="9" t="s">
-        <v>55</v>
-      </c>
       <c r="N2" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O2" s="15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P2" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q2" s="16">
         <v>21201</v>
       </c>
       <c r="R2" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="S2" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T2" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U2" s="17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V2" s="18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="W2" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="X2" s="19">
-        <f ca="1">L2</f>
+        <f>L2</f>
         <v>45761</v>
       </c>
       <c r="Y2" s="14">
-        <f ca="1">TODAY()+20</f>
+        <f>TODAY()+20</f>
         <v>45812</v>
       </c>
       <c r="Z2" s="20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AA2" s="21" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AB2" s="22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AC2" s="23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AD2" s="22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AE2" s="24">
         <v>124</v>
@@ -1257,262 +1235,284 @@
         <v>47</v>
       </c>
       <c r="AG2" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AH2" s="25">
         <v>40</v>
       </c>
       <c r="AI2" s="22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AJ2" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK2" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="AK2" s="19" t="s">
-        <v>72</v>
-      </c>
       <c r="AL2" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AM2" s="13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AN2" s="22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AO2" s="26" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AP2" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AQ2" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AR2" s="27" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AS2" s="28">
-        <f t="array" aca="1" ref="AS2:AS3" ca="1">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <f t="array" ref="AS2:AS3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
         <v>358004907</v>
       </c>
       <c r="AT2" s="22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AU2" s="29">
         <v>35591</v>
       </c>
       <c r="AV2" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AW2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AX2" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AY2" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AZ2" s="30">
         <v>54057</v>
       </c>
       <c r="BA2" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="K3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="BB2" t="s">
-        <v>83</v>
-      </c>
-      <c r="BC2" t="s">
-        <v>84</v>
-      </c>
-      <c r="BD2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:56" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="F3" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="I3" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="K3" s="26" t="s">
-        <v>61</v>
-      </c>
       <c r="L3" s="34">
-        <f t="shared" ref="L3" ca="1" si="0">TODAY()-31</f>
+        <f t="shared" ref="L3" si="0">TODAY()-31</f>
         <v>45761</v>
       </c>
       <c r="M3" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N3" s="35" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="O3" s="35" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P3" s="35" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q3" s="16">
         <v>21201</v>
       </c>
       <c r="R3" s="35" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="S3" s="35" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="T3" s="26" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="U3" s="26" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="V3" s="36" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="W3" s="26" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="X3" s="19">
-        <f t="shared" ref="X3" ca="1" si="1">L3</f>
+        <f t="shared" ref="X3" si="1">L3</f>
         <v>45761</v>
       </c>
       <c r="Y3" s="34">
-        <f t="shared" ref="Y3" ca="1" si="2">TODAY()+20</f>
+        <f t="shared" ref="Y3" si="2">TODAY()+20</f>
         <v>45812</v>
       </c>
       <c r="Z3" s="37" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AA3" s="38" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="AB3" s="39" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="AC3" s="40" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AD3" s="39" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="AE3" s="41">
         <v>121</v>
       </c>
       <c r="AF3" s="42" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="AG3" s="24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AH3" s="43">
         <v>10</v>
       </c>
       <c r="AI3" s="39" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AJ3" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK3" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="AK3" s="44" t="s">
-        <v>72</v>
-      </c>
       <c r="AL3" s="26" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AM3" s="26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AN3" s="39" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AO3" s="26" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AP3" s="26" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AQ3" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AR3" s="26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AS3" s="45">
-        <f ca="1"/>
         <v>573519542</v>
       </c>
       <c r="AT3" s="39" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AU3" s="46">
         <v>35226</v>
       </c>
       <c r="AV3" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AW3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AX3" s="26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="AY3" s="26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AZ3" s="30">
         <v>54057</v>
       </c>
       <c r="BA3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="BB3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="BC3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="BD3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2 Z2 W2 T2" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="8">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 Z3 W3 T3" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3">
       <formula1>INDIRECT($G3)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="V2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="V3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="V2" r:id="rId1"/>
+    <hyperlink ref="V3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
@@ -178,7 +178,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699096</t>
+    <t>10699547</t>
   </si>
   <si>
     <t>Passed</t>
@@ -193,10 +193,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Mariah</t>
-  </si>
-  <si>
-    <t>Tromp</t>
+    <t>Augustus</t>
+  </si>
+  <si>
+    <t>Beahan</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -226,7 +226,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 88181467</t>
+    <t>Auto 69342354</t>
   </si>
   <si>
     <t>Regular</t>
@@ -283,16 +283,16 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699097</t>
+    <t>10699548</t>
   </si>
   <si>
     <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
   </si>
   <si>
-    <t>Ewell</t>
-  </si>
-  <si>
-    <t>Bernhard</t>
+    <t>Johanna</t>
+  </si>
+  <si>
+    <t>Graham</t>
   </si>
   <si>
     <t>No</t>
@@ -399,7 +399,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -409,6 +409,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.5999938962981048"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -524,7 +530,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -532,8 +541,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -560,7 +569,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -580,7 +589,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -590,8 +599,8 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -600,14 +609,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -619,7 +628,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1097,7 +1106,7 @@
       <c r="AR1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AS1" s="7" t="s">
         <v>41</v>
       </c>
       <c r="AT1" s="3" t="s">
@@ -1141,158 +1150,158 @@
       <c r="B2" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="15">
         <f>TODAY()-31</f>
-        <v>45761</v>
-      </c>
-      <c r="M2" s="9" t="s">
+        <v>45779</v>
+      </c>
+      <c r="M2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="O2" s="15" t="s">
+      <c r="O2" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="Q2" s="17">
         <v>21201</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="R2" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="S2" s="13" t="s">
+      <c r="S2" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="T2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="U2" s="17" t="s">
+      <c r="U2" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="V2" s="18" t="s">
+      <c r="V2" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="W2" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="X2" s="19">
+      <c r="X2" s="20">
         <f>L2</f>
-        <v>45761</v>
-      </c>
-      <c r="Y2" s="14">
+        <v>45779</v>
+      </c>
+      <c r="Y2" s="15">
         <f>TODAY()+20</f>
-        <v>45812</v>
-      </c>
-      <c r="Z2" s="20" t="s">
+        <v>45830</v>
+      </c>
+      <c r="Z2" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AA2" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="AB2" s="22" t="s">
+      <c r="AB2" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="AC2" s="23" t="s">
+      <c r="AC2" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="AD2" s="22" t="s">
+      <c r="AD2" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="AE2" s="24">
+      <c r="AE2" s="25">
         <v>124</v>
       </c>
-      <c r="AF2" s="24" t="s">
+      <c r="AF2" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="AG2" s="24" t="s">
+      <c r="AG2" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="AH2" s="25">
+      <c r="AH2" s="26">
         <v>40</v>
       </c>
-      <c r="AI2" s="22" t="s">
+      <c r="AI2" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="AJ2" s="22" t="s">
+      <c r="AJ2" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="AK2" s="19" t="s">
+      <c r="AK2" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="AL2" s="13" t="s">
+      <c r="AL2" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="AM2" s="13" t="s">
+      <c r="AM2" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="AN2" s="22" t="s">
+      <c r="AN2" s="23" t="s">
         <v>79</v>
       </c>
-      <c r="AO2" s="26" t="s">
+      <c r="AO2" s="27" t="s">
         <v>80</v>
       </c>
-      <c r="AP2" s="9" t="s">
+      <c r="AP2" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AQ2" s="9" t="s">
+      <c r="AQ2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AR2" s="27" t="s">
+      <c r="AR2" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="AS2" s="28">
+      <c r="AS2" s="29">
         <f t="array" ref="AS2:AS3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>358004907</v>
-      </c>
-      <c r="AT2" s="22" t="s">
+        <v>854488220</v>
+      </c>
+      <c r="AT2" s="23" t="s">
         <v>83</v>
       </c>
-      <c r="AU2" s="29">
+      <c r="AU2" s="30">
         <v>35591</v>
       </c>
-      <c r="AV2" s="9" t="s">
+      <c r="AV2" s="10" t="s">
         <v>57</v>
       </c>
       <c r="AW2" t="s">
         <v>84</v>
       </c>
-      <c r="AX2" s="9" t="s">
+      <c r="AX2" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="AY2" s="9" t="s">
+      <c r="AY2" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="AZ2" s="30">
+      <c r="AZ2" s="31">
         <v>54057</v>
       </c>
       <c r="BA2" t="s">
@@ -1315,157 +1324,157 @@
       <c r="B3" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="I3" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="J3" s="26" t="s">
+      <c r="J3" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K3" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="L3" s="34">
+      <c r="L3" s="35">
         <f t="shared" ref="L3" si="0">TODAY()-31</f>
-        <v>45761</v>
-      </c>
-      <c r="M3" s="26" t="s">
+        <v>45779</v>
+      </c>
+      <c r="M3" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="N3" s="35" t="s">
+      <c r="N3" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="O3" s="35" t="s">
+      <c r="O3" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="P3" s="35" t="s">
+      <c r="P3" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="17">
         <v>21201</v>
       </c>
-      <c r="R3" s="35" t="s">
+      <c r="R3" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="S3" s="35" t="s">
+      <c r="S3" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="T3" s="26" t="s">
+      <c r="T3" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="U3" s="26" t="s">
+      <c r="U3" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="V3" s="36" t="s">
+      <c r="V3" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="W3" s="26" t="s">
+      <c r="W3" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="X3" s="19">
+      <c r="X3" s="20">
         <f t="shared" ref="X3" si="1">L3</f>
-        <v>45761</v>
-      </c>
-      <c r="Y3" s="34">
+        <v>45779</v>
+      </c>
+      <c r="Y3" s="35">
         <f t="shared" ref="Y3" si="2">TODAY()+20</f>
-        <v>45812</v>
-      </c>
-      <c r="Z3" s="37" t="s">
+        <v>45830</v>
+      </c>
+      <c r="Z3" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="AA3" s="38" t="s">
+      <c r="AA3" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="AB3" s="39" t="s">
+      <c r="AB3" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="AC3" s="40" t="s">
+      <c r="AC3" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="AD3" s="39" t="s">
+      <c r="AD3" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="AE3" s="41">
+      <c r="AE3" s="42">
         <v>121</v>
       </c>
-      <c r="AF3" s="42" t="s">
+      <c r="AF3" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="AG3" s="24" t="s">
+      <c r="AG3" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="AH3" s="43">
+      <c r="AH3" s="44">
         <v>10</v>
       </c>
-      <c r="AI3" s="39" t="s">
+      <c r="AI3" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="AJ3" s="39" t="s">
+      <c r="AJ3" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="AK3" s="44" t="s">
+      <c r="AK3" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="AL3" s="26" t="s">
+      <c r="AL3" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="AM3" s="26" t="s">
+      <c r="AM3" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="AN3" s="39" t="s">
+      <c r="AN3" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="AO3" s="26" t="s">
+      <c r="AO3" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="AP3" s="26" t="s">
+      <c r="AP3" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="AQ3" s="26" t="s">
+      <c r="AQ3" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="AR3" s="26" t="s">
+      <c r="AR3" s="27" t="s">
         <v>82</v>
       </c>
-      <c r="AS3" s="45">
-        <v>573519542</v>
-      </c>
-      <c r="AT3" s="39" t="s">
+      <c r="AS3" s="46">
+        <v>311108850</v>
+      </c>
+      <c r="AT3" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="AU3" s="46">
+      <c r="AU3" s="47">
         <v>35226</v>
       </c>
-      <c r="AV3" s="26" t="s">
+      <c r="AV3" s="27" t="s">
         <v>57</v>
       </c>
       <c r="AW3" t="s">
         <v>84</v>
       </c>
-      <c r="AX3" s="26" t="s">
+      <c r="AX3" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="AY3" s="26" t="s">
+      <c r="AY3" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="AZ3" s="30">
+      <c r="AZ3" s="31">
         <v>54057</v>
       </c>
       <c r="BA3" t="s">

--- a/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
@@ -178,7 +178,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699547</t>
+    <t>10699631</t>
   </si>
   <si>
     <t>Passed</t>
@@ -193,10 +193,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Augustus</t>
-  </si>
-  <si>
-    <t>Beahan</t>
+    <t>Rollin</t>
+  </si>
+  <si>
+    <t>Thompson</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -226,7 +226,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 69342354</t>
+    <t>Auto 24744288</t>
   </si>
   <si>
     <t>Regular</t>
@@ -283,16 +283,16 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699548</t>
+    <t>10699633</t>
   </si>
   <si>
     <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
   </si>
   <si>
-    <t>Johanna</t>
-  </si>
-  <si>
-    <t>Graham</t>
+    <t>Rebecca</t>
+  </si>
+  <si>
+    <t>Sporer</t>
   </si>
   <si>
     <t>No</t>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="L2" s="15">
         <f>TODAY()-31</f>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>57</v>
@@ -1216,11 +1216,11 @@
       </c>
       <c r="X2" s="20">
         <f>L2</f>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="Y2" s="15">
         <f>TODAY()+20</f>
-        <v>45830</v>
+        <v>45837</v>
       </c>
       <c r="Z2" s="21" t="s">
         <v>69</v>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="AS2" s="29">
         <f t="array" ref="AS2:AS3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>854488220</v>
+        <v>225001536</v>
       </c>
       <c r="AT2" s="23" t="s">
         <v>83</v>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="L3" s="35">
         <f t="shared" ref="L3" si="0">TODAY()-31</f>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="M3" s="27" t="s">
         <v>57</v>
@@ -1390,11 +1390,11 @@
       </c>
       <c r="X3" s="20">
         <f t="shared" ref="X3" si="1">L3</f>
-        <v>45779</v>
+        <v>45786</v>
       </c>
       <c r="Y3" s="35">
         <f t="shared" ref="Y3" si="2">TODAY()+20</f>
-        <v>45830</v>
+        <v>45837</v>
       </c>
       <c r="Z3" s="38" t="s">
         <v>69</v>
@@ -1454,7 +1454,7 @@
         <v>82</v>
       </c>
       <c r="AS3" s="46">
-        <v>311108850</v>
+        <v>988557136</v>
       </c>
       <c r="AT3" s="40" t="s">
         <v>83</v>

--- a/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
@@ -178,7 +178,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699631</t>
+    <t>10699753</t>
   </si>
   <si>
     <t>Passed</t>
@@ -193,10 +193,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Rollin</t>
-  </si>
-  <si>
-    <t>Thompson</t>
+    <t>Rylan</t>
+  </si>
+  <si>
+    <t>Heller</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -226,7 +226,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 24744288</t>
+    <t>Auto 66682893</t>
   </si>
   <si>
     <t>Regular</t>
@@ -283,16 +283,16 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699633</t>
+    <t>10699754</t>
   </si>
   <si>
     <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
   </si>
   <si>
-    <t>Rebecca</t>
-  </si>
-  <si>
-    <t>Sporer</t>
+    <t>Korbin</t>
+  </si>
+  <si>
+    <t>Stroman</t>
   </si>
   <si>
     <t>No</t>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="L2" s="15">
         <f>TODAY()-31</f>
-        <v>45786</v>
+        <v>45795</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>57</v>
@@ -1216,11 +1216,11 @@
       </c>
       <c r="X2" s="20">
         <f>L2</f>
-        <v>45786</v>
+        <v>45795</v>
       </c>
       <c r="Y2" s="15">
         <f>TODAY()+20</f>
-        <v>45837</v>
+        <v>45846</v>
       </c>
       <c r="Z2" s="21" t="s">
         <v>69</v>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="AS2" s="29">
         <f t="array" ref="AS2:AS3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>225001536</v>
+        <v>352276525</v>
       </c>
       <c r="AT2" s="23" t="s">
         <v>83</v>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="L3" s="35">
         <f t="shared" ref="L3" si="0">TODAY()-31</f>
-        <v>45786</v>
+        <v>45795</v>
       </c>
       <c r="M3" s="27" t="s">
         <v>57</v>
@@ -1390,11 +1390,11 @@
       </c>
       <c r="X3" s="20">
         <f t="shared" ref="X3" si="1">L3</f>
-        <v>45786</v>
+        <v>45795</v>
       </c>
       <c r="Y3" s="35">
         <f t="shared" ref="Y3" si="2">TODAY()+20</f>
-        <v>45837</v>
+        <v>45846</v>
       </c>
       <c r="Z3" s="38" t="s">
         <v>69</v>
@@ -1454,7 +1454,7 @@
         <v>82</v>
       </c>
       <c r="AS3" s="46">
-        <v>988557136</v>
+        <v>649131264</v>
       </c>
       <c r="AT3" s="40" t="s">
         <v>83</v>

--- a/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="117">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -178,10 +178,392 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699547</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t xml:space="preserve">Test failed for 'Karine Zemlak' Employee:{10699821}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('xpath=(//div[contains(@data-automation-id,"checkboxPanel")])[1]')[22m
+[2m  -   locator resolved to &lt;div class="WLDF WCFF" data-automation-id="checkboxPa…&gt;…&lt;/div&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div role="region" aria-hidden="false" aria-label="ac…&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
   <si>
     <t>124 Store Management (Gazuv Pemiku (10671950))</t>
@@ -193,10 +575,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Augustus</t>
-  </si>
-  <si>
-    <t>Beahan</t>
+    <t>Karine</t>
+  </si>
+  <si>
+    <t>Zemlak</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -226,97 +608,153 @@
     <t>New Hire</t>
   </si>
   <si>
+    <t>Auto 53080284</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Department Manager_NEW</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>4 Sales Workers - (EEO-1 Job Classifications-United States of America)</t>
+  </si>
+  <si>
+    <t>Default Work Shift (United States of America)</t>
+  </si>
+  <si>
+    <t>Automation Comments here….</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92 Retail Management </t>
+  </si>
+  <si>
+    <t xml:space="preserve">251 Management Retail </t>
+  </si>
+  <si>
+    <t>USA - Tier 2</t>
+  </si>
+  <si>
+    <t>Defaulted</t>
+  </si>
+  <si>
+    <t>Social Security Number (SSN)</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Employment Authorized</t>
+  </si>
+  <si>
+    <t>Audit Revealed that New Hire Was Not Run</t>
+  </si>
+  <si>
+    <t>USA Pay Group</t>
+  </si>
+  <si>
+    <t>Test_2</t>
+  </si>
+  <si>
+    <t>Test failed for 'Friedrich Blanda' Employee:{}Error: page.waitForTimeout: Test ended.</t>
+  </si>
+  <si>
+    <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
+  </si>
+  <si>
+    <t>Friedrich</t>
+  </si>
+  <si>
+    <t>Blanda</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Seasonal</t>
+  </si>
+  <si>
+    <t>Retail Assistant_NEW</t>
+  </si>
+  <si>
+    <t>Part time</t>
+  </si>
+  <si>
+    <t>Hourly</t>
+  </si>
+  <si>
+    <t>94 Retail Operative</t>
+  </si>
+  <si>
+    <t>01 Accessories</t>
+  </si>
+  <si>
+    <t>121 Walden Galleria</t>
+  </si>
+  <si>
+    <t>Test_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Cordia Koepp' Employee:{}Error: locator.click: Error: strict mode violation: locator('//a[text()="Hire Employee" and @data-uxi-rank="1"]') resolved to 2 elements:
+    1) &lt;a data-uxi-rank="1" class="pexsearch-1tbw0zn" data…&gt;Hire Employee&lt;/a&gt; aka locator('li').filter({ hasText: /^Hire EmployeePre-Hire$/ }).getByRole('link')
+    2) &lt;a data-uxi-rank="1" class="pexsearch-11mf54b" data…&gt;Hire Employee&lt;/a&gt; aka getByRole('link', { name: 'Hire Employee' }).nth(2)
+Call log:
+  [2m- waiting for locator('//a[text()="Hire Employee" and @data-uxi-rank="1"]')[22m
+</t>
+  </si>
+  <si>
+    <t>Cordia</t>
+  </si>
+  <si>
+    <t>Koepp</t>
+  </si>
+  <si>
+    <t>Auto 94898823</t>
+  </si>
+  <si>
+    <t>Test_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test failed for 'Amalia Boyer' Employee:{}Error: locator.click: Test ended.
+Call log:
+  [2m- waiting for locator('//a[text()="Hire Employee" and @data-uxi-rank="1"]')[22m
+</t>
+  </si>
+  <si>
+    <t>Amalia</t>
+  </si>
+  <si>
+    <t>Boyer</t>
+  </si>
+  <si>
+    <t>Test_5</t>
+  </si>
+  <si>
     <t>Auto 69342354</t>
   </si>
   <si>
-    <t>Regular</t>
-  </si>
-  <si>
-    <t>Department Manager_NEW</t>
-  </si>
-  <si>
-    <t>Full time</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>4 Sales Workers - (EEO-1 Job Classifications-United States of America)</t>
-  </si>
-  <si>
-    <t>Default Work Shift (United States of America)</t>
-  </si>
-  <si>
-    <t>Automation Comments here….</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92 Retail Management </t>
-  </si>
-  <si>
-    <t xml:space="preserve">251 Management Retail </t>
-  </si>
-  <si>
-    <t>USA - Tier 2</t>
-  </si>
-  <si>
-    <t>Defaulted</t>
-  </si>
-  <si>
-    <t>Social Security Number (SSN)</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>Employment Authorized</t>
-  </si>
-  <si>
-    <t>Audit Revealed that New Hire Was Not Run</t>
-  </si>
-  <si>
-    <t>USA Pay Group</t>
-  </si>
-  <si>
-    <t>Test_2</t>
-  </si>
-  <si>
-    <t>10699548</t>
-  </si>
-  <si>
-    <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
-  </si>
-  <si>
-    <t>Johanna</t>
-  </si>
-  <si>
-    <t>Graham</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Seasonal</t>
-  </si>
-  <si>
-    <t>Retail Assistant_NEW</t>
-  </si>
-  <si>
-    <t>Part time</t>
-  </si>
-  <si>
-    <t>Hourly</t>
-  </si>
-  <si>
-    <t>94 Retail Operative</t>
-  </si>
-  <si>
-    <t>01 Accessories</t>
-  </si>
-  <si>
-    <t>121 Walden Galleria</t>
+    <t>Test_6</t>
+  </si>
+  <si>
+    <t>Test_7</t>
+  </si>
+  <si>
+    <t>Test_8</t>
+  </si>
+  <si>
+    <t>Test_9</t>
+  </si>
+  <si>
+    <t>Test_10</t>
   </si>
 </sst>
 </file>
@@ -420,7 +858,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -914,63 +1352,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BD3"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <dimension ref="A1:BD11"/>
+  <sheetFormatPr defaultRowHeight="14.55" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" customWidth="1"/>
-    <col min="4" max="4" width="22.6328125" customWidth="1"/>
-    <col min="5" max="5" width="7.6328125" customWidth="1"/>
-    <col min="6" max="6" width="5.90625" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" customWidth="1"/>
-    <col min="8" max="8" width="11.81640625" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" customWidth="1"/>
-    <col min="11" max="11" width="5.26953125" customWidth="1"/>
-    <col min="12" max="12" width="15.90625" customWidth="1"/>
-    <col min="13" max="13" width="7.6328125" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" customWidth="1"/>
+    <col min="6" max="6" width="5.88671875" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="5.21875" customWidth="1"/>
+    <col min="12" max="12" width="15.88671875" customWidth="1"/>
+    <col min="13" max="13" width="7.6640625" customWidth="1"/>
     <col min="14" max="14" width="7" customWidth="1"/>
-    <col min="15" max="16" width="11.7265625" customWidth="1"/>
-    <col min="17" max="17" width="11.1796875" customWidth="1"/>
-    <col min="18" max="18" width="4.26953125" customWidth="1"/>
-    <col min="19" max="19" width="5.453125" customWidth="1"/>
-    <col min="20" max="20" width="5.26953125" customWidth="1"/>
-    <col min="21" max="21" width="7.36328125" customWidth="1"/>
-    <col min="22" max="22" width="13.08984375" customWidth="1"/>
-    <col min="23" max="23" width="5.26953125" customWidth="1"/>
-    <col min="24" max="24" width="15.54296875" customWidth="1"/>
-    <col min="25" max="25" width="17.1796875" customWidth="1"/>
-    <col min="26" max="26" width="7.6328125" customWidth="1"/>
+    <col min="15" max="16" width="11.77734375" customWidth="1"/>
+    <col min="17" max="17" width="11.21875" customWidth="1"/>
+    <col min="18" max="18" width="4.21875" customWidth="1"/>
+    <col min="19" max="19" width="5.44140625" customWidth="1"/>
+    <col min="20" max="20" width="5.21875" customWidth="1"/>
+    <col min="21" max="21" width="7.33203125" customWidth="1"/>
+    <col min="22" max="22" width="13.109375" customWidth="1"/>
+    <col min="23" max="23" width="5.21875" customWidth="1"/>
+    <col min="24" max="24" width="15.5546875" customWidth="1"/>
+    <col min="25" max="25" width="17.21875" customWidth="1"/>
+    <col min="26" max="26" width="7.6640625" customWidth="1"/>
     <col min="27" max="27" width="8" customWidth="1"/>
-    <col min="28" max="28" width="14.1796875" customWidth="1"/>
-    <col min="29" max="29" width="9.81640625" customWidth="1"/>
-    <col min="30" max="30" width="9.7265625" customWidth="1"/>
-    <col min="31" max="31" width="8.36328125" customWidth="1"/>
+    <col min="28" max="28" width="14.21875" customWidth="1"/>
+    <col min="29" max="30" width="9.77734375" customWidth="1"/>
+    <col min="31" max="31" width="8.33203125" customWidth="1"/>
     <col min="32" max="33" width="13" customWidth="1"/>
-    <col min="34" max="34" width="21.81640625" customWidth="1"/>
-    <col min="35" max="35" width="25.81640625" customWidth="1"/>
-    <col min="36" max="36" width="9.453125" customWidth="1"/>
-    <col min="37" max="37" width="19.54296875" customWidth="1"/>
-    <col min="38" max="38" width="10.36328125" customWidth="1"/>
-    <col min="39" max="39" width="10.81640625" customWidth="1"/>
-    <col min="40" max="40" width="17.81640625" customWidth="1"/>
+    <col min="34" max="34" width="21.77734375" customWidth="1"/>
+    <col min="35" max="35" width="25.77734375" customWidth="1"/>
+    <col min="36" max="36" width="9.44140625" customWidth="1"/>
+    <col min="37" max="37" width="19.5546875" customWidth="1"/>
+    <col min="38" max="38" width="10.33203125" customWidth="1"/>
+    <col min="39" max="39" width="10.77734375" customWidth="1"/>
+    <col min="40" max="40" width="17.77734375" customWidth="1"/>
     <col min="41" max="41" width="12" customWidth="1"/>
-    <col min="42" max="42" width="4.90625" customWidth="1"/>
-    <col min="43" max="43" width="8.7265625" customWidth="1"/>
-    <col min="44" max="45" width="15.6328125" customWidth="1"/>
-    <col min="46" max="46" width="7.26953125" customWidth="1"/>
-    <col min="47" max="47" width="14.1796875" customWidth="1"/>
-    <col min="48" max="48" width="13.90625" customWidth="1"/>
+    <col min="42" max="42" width="4.88671875" customWidth="1"/>
+    <col min="43" max="43" width="8.77734375" customWidth="1"/>
+    <col min="44" max="45" width="15.6640625" customWidth="1"/>
+    <col min="46" max="46" width="7.21875" customWidth="1"/>
+    <col min="47" max="47" width="14.21875" customWidth="1"/>
+    <col min="48" max="48" width="13.88671875" customWidth="1"/>
     <col min="49" max="49" width="14" customWidth="1"/>
     <col min="50" max="50" width="17" customWidth="1"/>
-    <col min="51" max="51" width="6.36328125" customWidth="1"/>
-    <col min="52" max="52" width="15.453125" customWidth="1"/>
-    <col min="53" max="53" width="14.7265625" customWidth="1"/>
-    <col min="54" max="54" width="30.453125" customWidth="1"/>
-    <col min="55" max="55" width="15.1796875" customWidth="1"/>
-    <col min="56" max="56" width="22.7265625" customWidth="1"/>
-    <col min="57" max="57" width="8.7265625" customWidth="1"/>
+    <col min="51" max="51" width="6.33203125" customWidth="1"/>
+    <col min="52" max="52" width="15.44140625" customWidth="1"/>
+    <col min="53" max="53" width="14.77734375" customWidth="1"/>
+    <col min="54" max="54" width="30.44140625" customWidth="1"/>
+    <col min="55" max="55" width="15.21875" customWidth="1"/>
+    <col min="56" max="56" width="22.77734375" customWidth="1"/>
+    <col min="57" max="57" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1143,7 +1580,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -1179,7 +1616,7 @@
       </c>
       <c r="L2" s="15">
         <f>TODAY()-31</f>
-        <v>45779</v>
+        <v>45801</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>57</v>
@@ -1216,11 +1653,11 @@
       </c>
       <c r="X2" s="20">
         <f>L2</f>
-        <v>45779</v>
+        <v>45801</v>
       </c>
       <c r="Y2" s="15">
         <f>TODAY()+20</f>
-        <v>45830</v>
+        <v>45852</v>
       </c>
       <c r="Z2" s="21" t="s">
         <v>69</v>
@@ -1281,7 +1718,7 @@
       </c>
       <c r="AS2" s="29">
         <f t="array" ref="AS2:AS3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>854488220</v>
+        <v>281089582</v>
       </c>
       <c r="AT2" s="23" t="s">
         <v>83</v>
@@ -1317,7 +1754,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="3" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>88</v>
       </c>
@@ -1352,8 +1789,8 @@
         <v>63</v>
       </c>
       <c r="L3" s="35">
-        <f t="shared" ref="L3" si="0">TODAY()-31</f>
-        <v>45779</v>
+        <f t="shared" ref="L3:L11" si="0">TODAY()-31</f>
+        <v>45801</v>
       </c>
       <c r="M3" s="27" t="s">
         <v>57</v>
@@ -1390,11 +1827,11 @@
       </c>
       <c r="X3" s="20">
         <f t="shared" ref="X3" si="1">L3</f>
-        <v>45779</v>
+        <v>45801</v>
       </c>
       <c r="Y3" s="35">
-        <f t="shared" ref="Y3" si="2">TODAY()+20</f>
-        <v>45830</v>
+        <f t="shared" ref="Y3:Y11" si="2">TODAY()+20</f>
+        <v>45852</v>
       </c>
       <c r="Z3" s="38" t="s">
         <v>69</v>
@@ -1454,7 +1891,7 @@
         <v>82</v>
       </c>
       <c r="AS3" s="46">
-        <v>311108850</v>
+        <v>370545812</v>
       </c>
       <c r="AT3" s="40" t="s">
         <v>83</v>
@@ -1490,36 +1927,1468 @@
         <v>87</v>
       </c>
     </row>
+    <row r="4" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="L4" s="15">
+        <f>TODAY()-31</f>
+        <v>45801</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="17">
+        <v>21201</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="S4" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="T4" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="U4" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="W4" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="X4" s="20">
+        <f>L4</f>
+        <v>45801</v>
+      </c>
+      <c r="Y4" s="15">
+        <f>TODAY()+20</f>
+        <v>45852</v>
+      </c>
+      <c r="Z4" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA4" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB4" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC4" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD4" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE4" s="25">
+        <v>124</v>
+      </c>
+      <c r="AF4" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG4" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH4" s="26">
+        <v>40</v>
+      </c>
+      <c r="AI4" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ4" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK4" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL4" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM4" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN4" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO4" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP4" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AQ4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR4" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS4" s="29">
+        <f t="array" ref="AS4:AS5">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>913363585</v>
+      </c>
+      <c r="AT4" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU4" s="30">
+        <v>35591</v>
+      </c>
+      <c r="AV4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY4" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ4" s="31">
+        <v>54057</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>108</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>109</v>
+      </c>
+      <c r="I5" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="L5" s="35">
+        <f t="shared" si="0"/>
+        <v>45801</v>
+      </c>
+      <c r="M5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="O5" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q5" s="17">
+        <v>21201</v>
+      </c>
+      <c r="R5" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="S5" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="T5" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="V5" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="W5" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="X5" s="20">
+        <f t="shared" ref="X5" si="3">L5</f>
+        <v>45801</v>
+      </c>
+      <c r="Y5" s="35">
+        <f t="shared" si="2"/>
+        <v>45852</v>
+      </c>
+      <c r="Z5" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA5" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB5" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC5" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD5" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE5" s="42">
+        <v>121</v>
+      </c>
+      <c r="AF5" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG5" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH5" s="44">
+        <v>10</v>
+      </c>
+      <c r="AI5" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ5" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK5" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL5" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM5" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN5" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="AO5" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP5" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR5" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS5" s="46">
+        <v>290136672</v>
+      </c>
+      <c r="AT5" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU5" s="47">
+        <v>35226</v>
+      </c>
+      <c r="AV5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY5" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ5" s="31">
+        <v>54057</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="12"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="L6" s="15">
+        <f>TODAY()-31</f>
+        <v>45801</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O6" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="P6" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q6" s="17">
+        <v>21201</v>
+      </c>
+      <c r="R6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="S6" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="U6" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="V6" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="W6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="X6" s="20">
+        <f>L6</f>
+        <v>45801</v>
+      </c>
+      <c r="Y6" s="15">
+        <f>TODAY()+20</f>
+        <v>45852</v>
+      </c>
+      <c r="Z6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA6" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB6" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC6" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD6" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE6" s="25">
+        <v>124</v>
+      </c>
+      <c r="AF6" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG6" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH6" s="26">
+        <v>40</v>
+      </c>
+      <c r="AI6" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ6" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK6" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL6" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM6" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN6" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO6" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP6" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AQ6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR6" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS6" s="29">
+        <f t="array" ref="AS6:AS7">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>661490362</v>
+      </c>
+      <c r="AT6" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU6" s="30">
+        <v>35591</v>
+      </c>
+      <c r="AV6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX6" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY6" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ6" s="31">
+        <v>54057</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G7" s="33"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="L7" s="35">
+        <f t="shared" si="0"/>
+        <v>45801</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="P7" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q7" s="17">
+        <v>21201</v>
+      </c>
+      <c r="R7" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="S7" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="T7" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="U7" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="V7" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="W7" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="X7" s="20">
+        <f t="shared" ref="X7" si="4">L7</f>
+        <v>45801</v>
+      </c>
+      <c r="Y7" s="35">
+        <f t="shared" si="2"/>
+        <v>45852</v>
+      </c>
+      <c r="Z7" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA7" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB7" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC7" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD7" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE7" s="42">
+        <v>121</v>
+      </c>
+      <c r="AF7" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG7" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH7" s="44">
+        <v>10</v>
+      </c>
+      <c r="AI7" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ7" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK7" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL7" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM7" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN7" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="AO7" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP7" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ7" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR7" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS7" s="46">
+        <v>432116339</v>
+      </c>
+      <c r="AT7" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU7" s="47">
+        <v>35226</v>
+      </c>
+      <c r="AV7" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX7" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY7" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ7" s="31">
+        <v>54057</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="12"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="L8" s="15">
+        <f>TODAY()-31</f>
+        <v>45801</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O8" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="17">
+        <v>21201</v>
+      </c>
+      <c r="R8" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="S8" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="T8" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="U8" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="V8" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="W8" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="X8" s="20">
+        <f>L8</f>
+        <v>45801</v>
+      </c>
+      <c r="Y8" s="15">
+        <f>TODAY()+20</f>
+        <v>45852</v>
+      </c>
+      <c r="Z8" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA8" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB8" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC8" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD8" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE8" s="25">
+        <v>124</v>
+      </c>
+      <c r="AF8" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG8" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH8" s="26">
+        <v>40</v>
+      </c>
+      <c r="AI8" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ8" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK8" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL8" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM8" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN8" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO8" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP8" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AQ8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR8" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS8" s="29">
+        <f t="array" ref="AS8:AS9">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>995847970</v>
+      </c>
+      <c r="AT8" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU8" s="30">
+        <v>35591</v>
+      </c>
+      <c r="AV8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX8" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY8" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ8" s="31">
+        <v>54057</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G9" s="33"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J9" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="L9" s="35">
+        <f t="shared" si="0"/>
+        <v>45801</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="O9" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="P9" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q9" s="17">
+        <v>21201</v>
+      </c>
+      <c r="R9" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="S9" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="T9" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="U9" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="V9" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="W9" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="X9" s="20">
+        <f t="shared" ref="X9" si="5">L9</f>
+        <v>45801</v>
+      </c>
+      <c r="Y9" s="35">
+        <f t="shared" si="2"/>
+        <v>45852</v>
+      </c>
+      <c r="Z9" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA9" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB9" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC9" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD9" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE9" s="42">
+        <v>121</v>
+      </c>
+      <c r="AF9" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG9" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH9" s="44">
+        <v>10</v>
+      </c>
+      <c r="AI9" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ9" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK9" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL9" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM9" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN9" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="AO9" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP9" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ9" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR9" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS9" s="46">
+        <v>361293561</v>
+      </c>
+      <c r="AT9" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU9" s="47">
+        <v>35226</v>
+      </c>
+      <c r="AV9" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX9" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY9" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ9" s="31">
+        <v>54057</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G10" s="12"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="15">
+        <f>TODAY()-31</f>
+        <v>45801</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O10" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="P10" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q10" s="17">
+        <v>21201</v>
+      </c>
+      <c r="R10" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="S10" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="T10" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="U10" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="V10" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="W10" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="X10" s="20">
+        <f>L10</f>
+        <v>45801</v>
+      </c>
+      <c r="Y10" s="15">
+        <f>TODAY()+20</f>
+        <v>45852</v>
+      </c>
+      <c r="Z10" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA10" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="AB10" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC10" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD10" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE10" s="25">
+        <v>124</v>
+      </c>
+      <c r="AF10" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG10" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH10" s="26">
+        <v>40</v>
+      </c>
+      <c r="AI10" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ10" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK10" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL10" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM10" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN10" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO10" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP10" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AQ10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR10" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS10" s="29">
+        <f t="array" ref="AS10:AS11">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>482996649</v>
+      </c>
+      <c r="AT10" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU10" s="30">
+        <v>35591</v>
+      </c>
+      <c r="AV10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY10" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ10" s="31">
+        <v>54057</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G11" s="33"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="35">
+        <f t="shared" si="0"/>
+        <v>45801</v>
+      </c>
+      <c r="M11" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="N11" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="O11" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="P11" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q11" s="17">
+        <v>21201</v>
+      </c>
+      <c r="R11" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="S11" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="T11" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="U11" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="V11" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="W11" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="X11" s="20">
+        <f t="shared" ref="X11" si="6">L11</f>
+        <v>45801</v>
+      </c>
+      <c r="Y11" s="35">
+        <f t="shared" si="2"/>
+        <v>45852</v>
+      </c>
+      <c r="Z11" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA11" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB11" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC11" s="41" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD11" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE11" s="42">
+        <v>121</v>
+      </c>
+      <c r="AF11" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG11" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH11" s="44">
+        <v>10</v>
+      </c>
+      <c r="AI11" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ11" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK11" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL11" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM11" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="AN11" s="40" t="s">
+        <v>99</v>
+      </c>
+      <c r="AO11" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="AP11" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ11" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR11" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS11" s="46">
+        <v>436499850</v>
+      </c>
+      <c r="AT11" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU11" s="47">
+        <v>35226</v>
+      </c>
+      <c r="AV11" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX11" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY11" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ11" s="31">
+        <v>54057</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="40">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K10">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K11">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3">
       <formula1>INDIRECT($G3)</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K6">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K7">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K8">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K9">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T11">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3">
       <formula1>INDIRECT($G3)</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T4">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T5">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T6">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T7">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T8">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T9">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W10">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W11">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3">
       <formula1>INDIRECT($G3)</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W4">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W5">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W6">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W7">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W8">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W9">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z10">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z11">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z4">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z5">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z6">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z7">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z8">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z9">
       <formula1>INDIRECT($G3)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="V2" r:id="rId1"/>
     <hyperlink ref="V3" r:id="rId2"/>
+    <hyperlink ref="V4" r:id="rId3"/>
+    <hyperlink ref="V5" r:id="rId4"/>
+    <hyperlink ref="V6" r:id="rId5"/>
+    <hyperlink ref="V7" r:id="rId6"/>
+    <hyperlink ref="V8" r:id="rId7"/>
+    <hyperlink ref="V9" r:id="rId8"/>
+    <hyperlink ref="V10" r:id="rId9"/>
+    <hyperlink ref="V11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
+    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="101">
   <si>
     <t>TestCaseID</t>
   </si>
@@ -178,10 +178,280 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699753</t>
-  </si>
-  <si>
-    <t>Passed</t>
+    <t xml:space="preserve">Test failed for 'Joelle Hayes' Employee:{10699822}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for locator('button:has-text("Submit")')[22m
+[2m  -   locator resolved to &lt;button type="button" title="Submit" class="WNWM WMDO WO…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WMT"&gt;…&lt;/div&gt; from &lt;div class="WAU WNT" data-automation-widget="wd-popup"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
   <si>
     <t>124 Store Management (Gazuv Pemiku (10671950))</t>
@@ -193,10 +463,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Rylan</t>
-  </si>
-  <si>
-    <t>Heller</t>
+    <t>Joelle</t>
+  </si>
+  <si>
+    <t>Hayes</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -226,97 +496,97 @@
     <t>New Hire</t>
   </si>
   <si>
+    <t>Auto 10307210</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t>Department Manager_NEW</t>
+  </si>
+  <si>
+    <t>Full time</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>4 Sales Workers - (EEO-1 Job Classifications-United States of America)</t>
+  </si>
+  <si>
+    <t>Default Work Shift (United States of America)</t>
+  </si>
+  <si>
+    <t>Automation Comments here….</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92 Retail Management </t>
+  </si>
+  <si>
+    <t xml:space="preserve">251 Management Retail </t>
+  </si>
+  <si>
+    <t>USA - Tier 2</t>
+  </si>
+  <si>
+    <t>Defaulted</t>
+  </si>
+  <si>
+    <t>Social Security Number (SSN)</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>Employment Authorized</t>
+  </si>
+  <si>
+    <t>Audit Revealed that New Hire Was Not Run</t>
+  </si>
+  <si>
+    <t>USA Pay Group</t>
+  </si>
+  <si>
+    <t>Test_2</t>
+  </si>
+  <si>
+    <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Seasonal</t>
+  </si>
+  <si>
+    <t>Retail Assistant_NEW</t>
+  </si>
+  <si>
+    <t>Part time</t>
+  </si>
+  <si>
+    <t>Hourly</t>
+  </si>
+  <si>
+    <t>94 Retail Operative</t>
+  </si>
+  <si>
+    <t>01 Accessories</t>
+  </si>
+  <si>
+    <t>121 Walden Galleria</t>
+  </si>
+  <si>
+    <t>Test_3</t>
+  </si>
+  <si>
     <t>Auto 66682893</t>
   </si>
   <si>
-    <t>Regular</t>
-  </si>
-  <si>
-    <t>Department Manager_NEW</t>
-  </si>
-  <si>
-    <t>Full time</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>4 Sales Workers - (EEO-1 Job Classifications-United States of America)</t>
-  </si>
-  <si>
-    <t>Default Work Shift (United States of America)</t>
-  </si>
-  <si>
-    <t>Automation Comments here….</t>
-  </si>
-  <si>
-    <t xml:space="preserve">92 Retail Management </t>
-  </si>
-  <si>
-    <t xml:space="preserve">251 Management Retail </t>
-  </si>
-  <si>
-    <t>USA - Tier 2</t>
-  </si>
-  <si>
-    <t>Defaulted</t>
-  </si>
-  <si>
-    <t>Social Security Number (SSN)</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>Employment Authorized</t>
-  </si>
-  <si>
-    <t>Audit Revealed that New Hire Was Not Run</t>
-  </si>
-  <si>
-    <t>USA Pay Group</t>
-  </si>
-  <si>
-    <t>Test_2</t>
-  </si>
-  <si>
-    <t>10699754</t>
-  </si>
-  <si>
-    <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
-  </si>
-  <si>
-    <t>Korbin</t>
-  </si>
-  <si>
-    <t>Stroman</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Seasonal</t>
-  </si>
-  <si>
-    <t>Retail Assistant_NEW</t>
-  </si>
-  <si>
-    <t>Part time</t>
-  </si>
-  <si>
-    <t>Hourly</t>
-  </si>
-  <si>
-    <t>94 Retail Operative</t>
-  </si>
-  <si>
-    <t>01 Accessories</t>
-  </si>
-  <si>
-    <t>121 Walden Galleria</t>
+    <t>Test_4</t>
   </si>
 </sst>
 </file>
@@ -420,7 +690,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FFFF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -914,63 +1184,62 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BD3"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
+  <dimension ref="A1:BD5"/>
+  <sheetFormatPr defaultRowHeight="14.55" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" customWidth="1"/>
-    <col min="3" max="3" width="9.36328125" customWidth="1"/>
-    <col min="4" max="4" width="22.6328125" customWidth="1"/>
-    <col min="5" max="5" width="7.6328125" customWidth="1"/>
-    <col min="6" max="6" width="5.90625" customWidth="1"/>
-    <col min="7" max="7" width="11.1796875" customWidth="1"/>
-    <col min="8" max="8" width="11.81640625" customWidth="1"/>
-    <col min="9" max="9" width="13.453125" customWidth="1"/>
-    <col min="10" max="10" width="12.54296875" customWidth="1"/>
-    <col min="11" max="11" width="5.26953125" customWidth="1"/>
-    <col min="12" max="12" width="15.90625" customWidth="1"/>
-    <col min="13" max="13" width="7.6328125" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" customWidth="1"/>
+    <col min="6" max="6" width="5.88671875" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" customWidth="1"/>
+    <col min="8" max="8" width="11.77734375" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" customWidth="1"/>
+    <col min="10" max="10" width="12.5546875" customWidth="1"/>
+    <col min="11" max="11" width="5.21875" customWidth="1"/>
+    <col min="12" max="12" width="15.88671875" customWidth="1"/>
+    <col min="13" max="13" width="7.6640625" customWidth="1"/>
     <col min="14" max="14" width="7" customWidth="1"/>
-    <col min="15" max="16" width="11.7265625" customWidth="1"/>
-    <col min="17" max="17" width="11.1796875" customWidth="1"/>
-    <col min="18" max="18" width="4.26953125" customWidth="1"/>
-    <col min="19" max="19" width="5.453125" customWidth="1"/>
-    <col min="20" max="20" width="5.26953125" customWidth="1"/>
-    <col min="21" max="21" width="7.36328125" customWidth="1"/>
-    <col min="22" max="22" width="13.08984375" customWidth="1"/>
-    <col min="23" max="23" width="5.26953125" customWidth="1"/>
-    <col min="24" max="24" width="15.54296875" customWidth="1"/>
-    <col min="25" max="25" width="17.1796875" customWidth="1"/>
-    <col min="26" max="26" width="7.6328125" customWidth="1"/>
+    <col min="15" max="16" width="11.77734375" customWidth="1"/>
+    <col min="17" max="17" width="11.21875" customWidth="1"/>
+    <col min="18" max="18" width="4.21875" customWidth="1"/>
+    <col min="19" max="19" width="5.44140625" customWidth="1"/>
+    <col min="20" max="20" width="5.21875" customWidth="1"/>
+    <col min="21" max="21" width="7.33203125" customWidth="1"/>
+    <col min="22" max="22" width="13.109375" customWidth="1"/>
+    <col min="23" max="23" width="5.21875" customWidth="1"/>
+    <col min="24" max="24" width="15.5546875" customWidth="1"/>
+    <col min="25" max="25" width="17.21875" customWidth="1"/>
+    <col min="26" max="26" width="7.6640625" customWidth="1"/>
     <col min="27" max="27" width="8" customWidth="1"/>
-    <col min="28" max="28" width="14.1796875" customWidth="1"/>
-    <col min="29" max="29" width="9.81640625" customWidth="1"/>
-    <col min="30" max="30" width="9.7265625" customWidth="1"/>
-    <col min="31" max="31" width="8.36328125" customWidth="1"/>
+    <col min="28" max="28" width="14.21875" customWidth="1"/>
+    <col min="29" max="30" width="9.77734375" customWidth="1"/>
+    <col min="31" max="31" width="8.33203125" customWidth="1"/>
     <col min="32" max="33" width="13" customWidth="1"/>
-    <col min="34" max="34" width="21.81640625" customWidth="1"/>
-    <col min="35" max="35" width="25.81640625" customWidth="1"/>
-    <col min="36" max="36" width="9.453125" customWidth="1"/>
-    <col min="37" max="37" width="19.54296875" customWidth="1"/>
-    <col min="38" max="38" width="10.36328125" customWidth="1"/>
-    <col min="39" max="39" width="10.81640625" customWidth="1"/>
-    <col min="40" max="40" width="17.81640625" customWidth="1"/>
+    <col min="34" max="34" width="21.77734375" customWidth="1"/>
+    <col min="35" max="35" width="25.77734375" customWidth="1"/>
+    <col min="36" max="36" width="9.44140625" customWidth="1"/>
+    <col min="37" max="37" width="19.5546875" customWidth="1"/>
+    <col min="38" max="38" width="10.33203125" customWidth="1"/>
+    <col min="39" max="39" width="10.77734375" customWidth="1"/>
+    <col min="40" max="40" width="17.77734375" customWidth="1"/>
     <col min="41" max="41" width="12" customWidth="1"/>
-    <col min="42" max="42" width="4.90625" customWidth="1"/>
-    <col min="43" max="43" width="8.7265625" customWidth="1"/>
-    <col min="44" max="45" width="15.6328125" customWidth="1"/>
-    <col min="46" max="46" width="7.26953125" customWidth="1"/>
-    <col min="47" max="47" width="14.1796875" customWidth="1"/>
-    <col min="48" max="48" width="13.90625" customWidth="1"/>
+    <col min="42" max="42" width="4.88671875" customWidth="1"/>
+    <col min="43" max="43" width="8.77734375" customWidth="1"/>
+    <col min="44" max="45" width="15.6640625" customWidth="1"/>
+    <col min="46" max="46" width="7.21875" customWidth="1"/>
+    <col min="47" max="47" width="14.21875" customWidth="1"/>
+    <col min="48" max="48" width="13.88671875" customWidth="1"/>
     <col min="49" max="49" width="14" customWidth="1"/>
     <col min="50" max="50" width="17" customWidth="1"/>
-    <col min="51" max="51" width="6.36328125" customWidth="1"/>
-    <col min="52" max="52" width="15.453125" customWidth="1"/>
-    <col min="53" max="53" width="14.7265625" customWidth="1"/>
-    <col min="54" max="54" width="30.453125" customWidth="1"/>
-    <col min="55" max="55" width="15.1796875" customWidth="1"/>
-    <col min="56" max="56" width="22.7265625" customWidth="1"/>
-    <col min="57" max="57" width="8.7265625" customWidth="1"/>
+    <col min="51" max="51" width="6.33203125" customWidth="1"/>
+    <col min="52" max="52" width="15.44140625" customWidth="1"/>
+    <col min="53" max="53" width="14.77734375" customWidth="1"/>
+    <col min="54" max="54" width="30.44140625" customWidth="1"/>
+    <col min="55" max="55" width="15.21875" customWidth="1"/>
+    <col min="56" max="56" width="22.77734375" customWidth="1"/>
+    <col min="57" max="57" width="8.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" spans="1:56" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -1143,7 +1412,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="2" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -1179,7 +1448,7 @@
       </c>
       <c r="L2" s="15">
         <f>TODAY()-31</f>
-        <v>45795</v>
+        <v>45801</v>
       </c>
       <c r="M2" s="10" t="s">
         <v>57</v>
@@ -1216,11 +1485,11 @@
       </c>
       <c r="X2" s="20">
         <f>L2</f>
-        <v>45795</v>
+        <v>45801</v>
       </c>
       <c r="Y2" s="15">
         <f>TODAY()+20</f>
-        <v>45846</v>
+        <v>45852</v>
       </c>
       <c r="Z2" s="21" t="s">
         <v>69</v>
@@ -1281,7 +1550,7 @@
       </c>
       <c r="AS2" s="29">
         <f t="array" ref="AS2:AS3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>352276525</v>
+        <v>605144298</v>
       </c>
       <c r="AT2" s="23" t="s">
         <v>83</v>
@@ -1317,18 +1586,13 @@
         <v>87</v>
       </c>
     </row>
-    <row r="3" ht="14.5" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+    <row r="3" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>88</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>57</v>
@@ -1336,12 +1600,8 @@
       <c r="F3" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="33" t="s">
-        <v>91</v>
-      </c>
-      <c r="H3" s="34" t="s">
-        <v>92</v>
-      </c>
+      <c r="G3" s="33"/>
+      <c r="H3" s="34"/>
       <c r="I3" s="27" t="s">
         <v>61</v>
       </c>
@@ -1352,8 +1612,8 @@
         <v>63</v>
       </c>
       <c r="L3" s="35">
-        <f t="shared" ref="L3" si="0">TODAY()-31</f>
-        <v>45795</v>
+        <f t="shared" ref="L3:L5" si="0">TODAY()-31</f>
+        <v>45801</v>
       </c>
       <c r="M3" s="27" t="s">
         <v>57</v>
@@ -1390,32 +1650,32 @@
       </c>
       <c r="X3" s="20">
         <f t="shared" ref="X3" si="1">L3</f>
-        <v>45795</v>
+        <v>45801</v>
       </c>
       <c r="Y3" s="35">
-        <f t="shared" ref="Y3" si="2">TODAY()+20</f>
-        <v>45846</v>
+        <f t="shared" ref="Y3:Y5" si="2">TODAY()+20</f>
+        <v>45852</v>
       </c>
       <c r="Z3" s="38" t="s">
         <v>69</v>
       </c>
       <c r="AA3" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB3" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC3" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD3" s="40" t="s">
         <v>93</v>
-      </c>
-      <c r="AB3" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="AC3" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="AD3" s="40" t="s">
-        <v>96</v>
       </c>
       <c r="AE3" s="42">
         <v>121</v>
       </c>
       <c r="AF3" s="43" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AG3" s="25" t="s">
         <v>74</v>
@@ -1436,13 +1696,13 @@
         <v>77</v>
       </c>
       <c r="AM3" s="27" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AN3" s="40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="AO3" s="27" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AP3" s="27" t="s">
         <v>74</v>
@@ -1454,7 +1714,7 @@
         <v>82</v>
       </c>
       <c r="AS3" s="46">
-        <v>649131264</v>
+        <v>697866561</v>
       </c>
       <c r="AT3" s="40" t="s">
         <v>83</v>
@@ -1490,12 +1750,345 @@
         <v>87</v>
       </c>
     </row>
+    <row r="4" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" s="12"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="L4" s="15">
+        <f>TODAY()-31</f>
+        <v>45801</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="O4" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="P4" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="17">
+        <v>21201</v>
+      </c>
+      <c r="R4" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="S4" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="T4" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="U4" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="V4" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="W4" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="X4" s="20">
+        <f>L4</f>
+        <v>45801</v>
+      </c>
+      <c r="Y4" s="15">
+        <f>TODAY()+20</f>
+        <v>45852</v>
+      </c>
+      <c r="Z4" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA4" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB4" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="AC4" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="AD4" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="AE4" s="25">
+        <v>124</v>
+      </c>
+      <c r="AF4" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG4" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH4" s="26">
+        <v>40</v>
+      </c>
+      <c r="AI4" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ4" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK4" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL4" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM4" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="AN4" s="23" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO4" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="AP4" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AQ4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR4" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS4" s="29">
+        <f t="array" ref="AS4:AS5">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
+        <v>852193041</v>
+      </c>
+      <c r="AT4" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU4" s="30">
+        <v>35591</v>
+      </c>
+      <c r="AV4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX4" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY4" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ4" s="31">
+        <v>54057</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" ht="14.55" customHeight="1" spans="1:56" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="33"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="K5" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="L5" s="35">
+        <f t="shared" si="0"/>
+        <v>45801</v>
+      </c>
+      <c r="M5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="O5" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q5" s="17">
+        <v>21201</v>
+      </c>
+      <c r="R5" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="S5" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="T5" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="V5" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="W5" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="X5" s="20">
+        <f t="shared" ref="X5" si="3">L5</f>
+        <v>45801</v>
+      </c>
+      <c r="Y5" s="35">
+        <f t="shared" si="2"/>
+        <v>45852</v>
+      </c>
+      <c r="Z5" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA5" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="AB5" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC5" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD5" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="AE5" s="42">
+        <v>121</v>
+      </c>
+      <c r="AF5" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="AG5" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH5" s="44">
+        <v>10</v>
+      </c>
+      <c r="AI5" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="AJ5" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK5" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="AL5" s="27" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM5" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="AN5" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO5" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP5" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AR5" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AS5" s="46">
+        <v>309703275</v>
+      </c>
+      <c r="AT5" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU5" s="47">
+        <v>35226</v>
+      </c>
+      <c r="AV5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AX5" s="27" t="s">
+        <v>57</v>
+      </c>
+      <c r="AY5" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="AZ5" s="31">
+        <v>54057</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>86</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="8">
+  <dataValidations count="16">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K2">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K4">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K5">
       <formula1>INDIRECT($G3)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T2">
@@ -1504,10 +2097,22 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T3">
       <formula1>INDIRECT($G3)</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T4">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T5">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W2">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W3">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W4">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="W5">
       <formula1>INDIRECT($G3)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z2">
@@ -1516,10 +2121,18 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z3">
       <formula1>INDIRECT($G3)</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z4">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z5">
+      <formula1>INDIRECT($G3)</formula1>
+    </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="V2" r:id="rId1"/>
     <hyperlink ref="V3" r:id="rId2"/>
+    <hyperlink ref="V4" r:id="rId3"/>
+    <hyperlink ref="V5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>

--- a/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_USA_Regression_PK17.xlsx
@@ -178,7 +178,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10700283</t>
+    <t>10700471</t>
   </si>
   <si>
     <t>Passed</t>
@@ -193,10 +193,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Orville</t>
-  </si>
-  <si>
-    <t>Turcotte</t>
+    <t>Janelle</t>
+  </si>
+  <si>
+    <t>Wolf</t>
   </si>
   <si>
     <t>(202) 555-0147</t>
@@ -226,7 +226,7 @@
     <t>New Hire</t>
   </si>
   <si>
-    <t>Auto 10358277</t>
+    <t>Auto 32767878</t>
   </si>
   <si>
     <t>Regular</t>
@@ -283,16 +283,16 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10700268</t>
+    <t>10700467</t>
   </si>
   <si>
     <t>121 Recruitment (Ginyv Lypevo (10498025))</t>
   </si>
   <si>
-    <t>Kevin</t>
-  </si>
-  <si>
-    <t>Feest</t>
+    <t>Ellsworth</t>
+  </si>
+  <si>
+    <t>Gorczany</t>
   </si>
   <si>
     <t>No</t>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="L2" s="16">
         <f>TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M2" s="11" t="s">
         <v>57</v>
@@ -1219,11 +1219,11 @@
       </c>
       <c r="X2" s="21">
         <f>L2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="Y2" s="16">
         <f>TODAY()+20</f>
-        <v>45873</v>
+        <v>45894</v>
       </c>
       <c r="Z2" s="22" t="s">
         <v>69</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AS2" s="30">
         <f t="array" ref="AS2:AS3">_xlfn.RANDARRAY(2,1,123456789,999999999,TRUE)</f>
-        <v>873062303</v>
+        <v>966207480</v>
       </c>
       <c r="AT2" s="24" t="s">
         <v>83</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L3" s="36">
         <f t="shared" ref="L3" si="0">TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M3" s="28" t="s">
         <v>57</v>
@@ -1393,11 +1393,11 @@
       </c>
       <c r="X3" s="21">
         <f t="shared" ref="X3" si="1">L3</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="Y3" s="36">
         <f t="shared" ref="Y3" si="2">TODAY()+20</f>
-        <v>45873</v>
+        <v>45894</v>
       </c>
       <c r="Z3" s="39" t="s">
         <v>69</v>
@@ -1457,7 +1457,7 @@
         <v>82</v>
       </c>
       <c r="AS3" s="47">
-        <v>949795620</v>
+        <v>236805149</v>
       </c>
       <c r="AT3" s="41" t="s">
         <v>83</v>
